--- a/Result/profitability/6182.xlsx
+++ b/Result/profitability/6182.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.39625</v>
+        <v>0.40125</v>
       </c>
       <c r="N2" t="n">
-        <v>25.31</v>
+        <v>24.94</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.515</v>
+        <v>0.5225</v>
       </c>
       <c r="N3" t="n">
-        <v>26.135</v>
+        <v>26.07</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>0.7125</v>
       </c>
       <c r="N4" t="n">
-        <v>27.6275</v>
+        <v>27.86375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.84</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6012500000000001</v>
+        <v>0.62625</v>
       </c>
       <c r="N5" t="n">
-        <v>19.33625</v>
+        <v>19.13875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5575</v>
+        <v>0.55875</v>
       </c>
       <c r="N6" t="n">
-        <v>14.7425</v>
+        <v>14.65125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4462499999999999</v>
+        <v>0.4337500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>10.30125</v>
+        <v>9.5375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.43625</v>
+        <v>0.4425</v>
       </c>
       <c r="N8" t="n">
-        <v>9.10125</v>
+        <v>9.552500000000002</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2712</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2098</v>
+      </c>
+      <c r="E75" t="n">
+        <v>614</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>91</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>76</v>
+      </c>
+      <c r="K75" t="n">
+        <v>31</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1897004729374672</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.579999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06523534269199005</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
